--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,6 +909,103 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128686994</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91464</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hucksjöåsberget, Hucksjöåsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546980</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6968917</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>128686994</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97364978</v>
+        <v>128686994</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hucksjöåsberget, Jmt</t>
+          <t>Hucksjöåsberget, Hucksjöåsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546983.2806783094</v>
+        <v>546980</v>
       </c>
       <c r="R2" t="n">
-        <v>6968935.482811945</v>
+        <v>6968917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,53 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Vincent Heldt Cassel</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97364945</v>
+        <v>97364949</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546983.0384934883</v>
+        <v>547036</v>
       </c>
       <c r="R3" t="n">
-        <v>6968952.381256543</v>
+        <v>6968881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,21 +840,11 @@
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -890,7 +856,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128686994</v>
+        <v>97364945</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hucksjöåsberget, Hucksjöåsberget, Jmt</t>
+          <t>Hucksjöåsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546980</v>
+        <v>546983</v>
       </c>
       <c r="R4" t="n">
-        <v>6968917</v>
+        <v>6968952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,19 +959,341 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Vincent Heldt Cassel</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Vincent Heldt Cassel</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97364950</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hucksjöåsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6968881</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97364978</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hucksjöåsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546984</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6968935</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97364939</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hucksjöåsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6968881</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19437-2023 artfynd.xlsx
+++ b/artfynd/A 19437-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128686994</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364950</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,8 +1324,21 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>